--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="485">
   <si>
     <t>Filename</t>
   </si>
@@ -808,16 +808,19 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9797,0.0006,0.0083,0.0031</t>
-  </si>
-  <si>
-    <t>0.0080,0.0003,0.0036,0.9949</t>
-  </si>
-  <si>
-    <t>0.9821,0.0001,0.0004,0.0168</t>
-  </si>
-  <si>
-    <t>0.3140,0.0000,0.0019,0.8619</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9748,0.0010,0.0119,0.0030</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0010,0.9995</t>
+  </si>
+  <si>
+    <t>0.9024,0.0001,0.0001,0.1754</t>
+  </si>
+  <si>
+    <t>0.0440,0.0000,0.0002,0.9932</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
@@ -826,634 +829,646 @@
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9946,0.0004,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0079,0.0025,0.9904,0.0003</t>
+  </si>
+  <si>
+    <t>0.9940,0.0001,0.0062,0.0000</t>
+  </si>
+  <si>
+    <t>0.0512,0.0025,0.9564,0.0002</t>
+  </si>
+  <si>
+    <t>0.9735,0.0016,0.0213,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.9952,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9223,0.0001,0.0750,0.0014</t>
+  </si>
+  <si>
+    <t>0.7344,0.0018,0.2644,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0031,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0017,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9860,0.0058,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0009</t>
+  </si>
+  <si>
+    <t>0.0251,0.9201,0.0095,0.0000</t>
+  </si>
+  <si>
+    <t>0.9797,0.0001,0.0161,0.0002</t>
+  </si>
+  <si>
+    <t>0.6412,0.0006,0.3636,0.0004</t>
+  </si>
+  <si>
+    <t>0.2171,0.8511,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0063,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0851,0.0010,0.9253,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0083,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0063,0.0003,0.9935,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.3144,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.0992,0.0003,0.9897</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0041,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0096,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1644,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9981,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0109,0.0003,0.9922,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9996,0.0007</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9980,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9932,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0022,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0228,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9951,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9976,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9986,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9840,0.0005,0.0178,0.0001</t>
+  </si>
+  <si>
+    <t>0.8554,0.0086,0.1054,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9973,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9147,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9964,0.0173,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.6640,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0002,0.1237,0.9746</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0004,0.9999</t>
+  </si>
+  <si>
+    <t>0.0019,0.0003,0.0020,0.9983</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0009,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0050,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9873,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9736,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9640,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9687,0.9897,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9695,0.9731,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
     <t>0.9993,0.0004,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0016,0.9984,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9983,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.3089,0.7534,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.5405,0.0091,0.4283,0.0063</t>
+  </si>
+  <si>
+    <t>0.8858,0.0010,0.1265,0.0002</t>
+  </si>
+  <si>
+    <t>0.6080,0.0094,0.3142,0.0029</t>
+  </si>
+  <si>
+    <t>0.7699,0.0022,0.2402,0.0007</t>
+  </si>
+  <si>
+    <t>0.0043,0.0008,0.0196,0.9896</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0047,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9835,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9709,0.0316,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9138,0.1266,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1711,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0301,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0227,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0012,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9891,0.0005,0.0057,0.0007</t>
+  </si>
+  <si>
+    <t>0.1396,0.0005,0.8874,0.0011</t>
+  </si>
+  <si>
+    <t>0.9571,0.0050,0.0177,0.0015</t>
+  </si>
+  <si>
+    <t>0.0045,0.0000,0.0002,0.9987</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0005,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0111,0.9856,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.6611,0.4386,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.4884,0.0000,0.0001,0.8971</t>
+  </si>
+  <si>
+    <t>0.0003,0.0374,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.1074,0.8555,0.0270,0.0011</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.5694,0.4039,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.9744,0.0077,0.0095,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0027,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.7627,0.3017,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.6313,0.4503,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.6328,0.4764,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0021,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9684,0.0222,0.0021,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0013,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0064,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.0106,0.9891,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0242,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0975,0.0000,0.9731,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.4471,0.0089,0.5297,0.0014</t>
+  </si>
+  <si>
+    <t>0.0008,0.0007,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.9784,0.0011,0.0101,0.0011</t>
+  </si>
+  <si>
+    <t>0.3957,0.0186,0.5251,0.0014</t>
+  </si>
+  <si>
+    <t>0.4718,0.3441,0.0232,0.0003</t>
+  </si>
+  <si>
+    <t>0.6601,0.0038,0.3110,0.0001</t>
+  </si>
+  <si>
+    <t>0.9751,0.0004,0.0268,0.0002</t>
+  </si>
+  <si>
+    <t>0.1966,0.0132,0.7392,0.0030</t>
+  </si>
+  <si>
+    <t>0.7432,0.3412,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0273,0.9780,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.3123,0.8019,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7816,0.2912,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8372,0.2195,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9310,0.0139,0.0164,0.0015</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9823,0.0009,0.0017,0.0023</t>
+  </si>
+  <si>
+    <t>0.9339,0.0053,0.0329,0.0035</t>
+  </si>
+  <si>
+    <t>0.9935,0.0003,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9977,0.0053</t>
+  </si>
+  <si>
+    <t>0.0027,0.0023,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.2098,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0570,0.0055,0.9216,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0080,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9677,0.0343,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9925,0.0084,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0058,0.0475,0.9790,0.0006</t>
+  </si>
+  <si>
+    <t>0.9318,0.0009,0.0776,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0480,0.9939,0.0001</t>
+  </si>
+  <si>
+    <t>0.0058,0.0003,0.9940,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.0017,0.9905,0.0011</t>
+  </si>
+  <si>
+    <t>0.9402,0.0067,0.0368,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0001,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9973,0.0001,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0176,0.0028,0.9853,0.0002</t>
-  </si>
-  <si>
-    <t>0.6458,0.0003,0.4987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0012,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.9525,0.0020,0.0421,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.9938,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0123,0.0007,0.9852,0.0014</t>
-  </si>
-  <si>
-    <t>0.7374,0.0011,0.2911,0.0021</t>
-  </si>
-  <si>
-    <t>0.0022,0.0005,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0640,0.0071,0.9030,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.0001,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.0003,0.9945,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0032,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.2991,0.0499,0.4170,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0127,0.9757,0.0062,0.0000</t>
-  </si>
-  <si>
-    <t>0.6578,0.0012,0.2951,0.0025</t>
-  </si>
-  <si>
-    <t>0.5817,0.0010,0.4405,0.0002</t>
-  </si>
-  <si>
-    <t>0.3722,0.7101,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0048,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.8840,0.2292,0.0008</t>
-  </si>
-  <si>
-    <t>0.0082,0.0012,0.9866,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0216,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0084,0.0003,0.9885,0.0015</t>
-  </si>
-  <si>
-    <t>0.0011,0.0110,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0670,0.0003,0.9982</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0036,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0132,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7221,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9984,0.0015</t>
-  </si>
-  <si>
-    <t>0.0017,0.0002,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0063,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0030,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0079,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9818,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0062,0.9955,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9985,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0007,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.1380,0.0236,0.7852,0.0037</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9955,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9910,0.9894,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0204,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9951,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0001,0.0830,0.9695</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0003,0.9995</t>
-  </si>
-  <si>
-    <t>0.0039,0.0011,0.0004,0.9980</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0025,0.9989</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0536,0.9980</t>
-  </si>
-  <si>
-    <t>0.0000,0.9908,0.9777,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9664,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9978,0.1496,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9531,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9867,0.9952,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9946,0.0077,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0018,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.9827,0.0003,0.0136,0.0003</t>
-  </si>
-  <si>
-    <t>0.0082,0.0002,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.9902,0.0211,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1435,0.8807,0.0075,0.0004</t>
-  </si>
-  <si>
-    <t>0.8258,0.0023,0.1854,0.0027</t>
-  </si>
-  <si>
-    <t>0.6394,0.0009,0.4474,0.0003</t>
-  </si>
-  <si>
-    <t>0.3474,0.4010,0.0323,0.0085</t>
-  </si>
-  <si>
-    <t>0.8484,0.0033,0.1387,0.0004</t>
-  </si>
-  <si>
-    <t>0.0020,0.0014,0.0015,0.9978</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.9623,0.9525,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9722,0.0289,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.8226,0.2450,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3632,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.7580,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0570,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0030,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0013,0.0132,0.0006</t>
-  </si>
-  <si>
-    <t>0.2817,0.0007,0.7714,0.0018</t>
-  </si>
-  <si>
-    <t>0.9680,0.0033,0.0139,0.0011</t>
-  </si>
-  <si>
-    <t>0.0331,0.0000,0.0004,0.9916</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0040,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0314,0.9674,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.2337,0.8300,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0000,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.2103,0.0000,0.0000,0.9809</t>
-  </si>
-  <si>
-    <t>0.0002,0.0186,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.9969,0.0000,0.0003,0.0028</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.2485,0.7460,0.0050,0.0020</t>
-  </si>
-  <si>
-    <t>0.9947,0.0008,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.5914,0.2933,0.0142,0.0052</t>
-  </si>
-  <si>
-    <t>0.9931,0.0017,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9775,0.0096,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.4687,0.6191,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.7085,0.3481,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.6907,0.3852,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.0957,0.0540,0.8341,0.0003</t>
-  </si>
-  <si>
-    <t>0.9940,0.0055,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9780,0.0160,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9830,0.0096,0.0042,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0055,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0008,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0024,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.0002,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.3089,0.0022,0.7517,0.0010</t>
-  </si>
-  <si>
-    <t>0.0028,0.0009,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.5958,0.0098,0.3740,0.0016</t>
-  </si>
-  <si>
-    <t>0.3162,0.0077,0.6460,0.0007</t>
-  </si>
-  <si>
-    <t>0.0754,0.7400,0.0904,0.0002</t>
-  </si>
-  <si>
-    <t>0.3855,0.0019,0.6384,0.0001</t>
-  </si>
-  <si>
-    <t>0.9564,0.0019,0.0353,0.0006</t>
-  </si>
-  <si>
-    <t>0.6561,0.0307,0.1724,0.0090</t>
-  </si>
-  <si>
-    <t>0.1510,0.8888,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0192,0.9885,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.1456,0.9091,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9897,0.0119,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0142,0.9868,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9892,0.0017,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9910,0.0005,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.7949,0.0220,0.1241,0.0023</t>
-  </si>
-  <si>
-    <t>0.9147,0.0029,0.0790,0.0007</t>
-  </si>
-  <si>
-    <t>0.0123,0.0015,0.9879,0.0019</t>
-  </si>
-  <si>
-    <t>0.0021,0.1833,0.9630,0.0005</t>
-  </si>
-  <si>
-    <t>0.0013,0.0979,0.9937,0.0002</t>
-  </si>
-  <si>
-    <t>0.0390,0.0013,0.9662,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0174,0.9946,0.0001</t>
-  </si>
-  <si>
-    <t>0.9934,0.0048,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.2459,0.1302,0.4162,0.0016</t>
-  </si>
-  <si>
-    <t>0.3050,0.0005,0.7788,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0112,0.0053,0.9863,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0066,0.0005,0.9922,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0005,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0057,0.9981,0.0011</t>
-  </si>
-  <si>
-    <t>0.9319,0.0026,0.0561,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0046,0.9915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0102,0.0941,0.9016,0.0005</t>
-  </si>
-  <si>
-    <t>0.0057,0.0212,0.9730,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0876,0.0015,0.7615,0.0746</t>
-  </si>
-  <si>
-    <t>0.0054,0.0030,0.9895,0.0018</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.8095,0.0000,0.0020,0.3602</t>
-  </si>
-  <si>
-    <t>0.0020,0.0138,0.0004,0.9982</t>
-  </si>
-  <si>
-    <t>0.0031,0.0002,0.0115,0.9945</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.3592,0.0001,0.0096,0.6929</t>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0065,0.0069,0.9891,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.0620,0.9595,0.0004</t>
+  </si>
+  <si>
+    <t>0.0316,0.0201,0.9158,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0310,0.0042,0.9589,0.0046</t>
+  </si>
+  <si>
+    <t>0.0097,0.0012,0.9849,0.0015</t>
+  </si>
+  <si>
+    <t>0.0063,0.0014,0.9887,0.0008</t>
+  </si>
+  <si>
+    <t>0.9922,0.0000,0.0008,0.0105</t>
+  </si>
+  <si>
+    <t>0.0148,0.0013,0.0072,0.9867</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0009,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.1569,0.0003,0.0024,0.9295</t>
   </si>
 </sst>
 </file>
@@ -1839,7 +1854,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1853,7 +1868,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1867,7 +1882,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1881,7 +1896,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1895,7 +1910,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1909,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1923,7 +1938,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1937,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1951,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1965,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1979,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1993,7 +2008,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2007,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2021,7 +2036,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2035,7 +2050,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2049,7 +2064,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2063,7 +2078,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2077,7 +2092,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2091,7 +2106,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2105,7 +2120,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2119,7 +2134,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2133,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2144,10 +2159,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2161,7 +2176,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2175,7 +2190,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2189,7 +2204,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2203,7 +2218,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2217,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2231,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2245,7 +2260,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2259,7 +2274,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2273,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2287,7 +2302,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2301,7 +2316,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2315,7 +2330,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2329,7 +2344,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2343,7 +2358,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2354,10 +2369,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2371,7 +2386,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2385,7 +2400,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2399,7 +2414,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2413,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2427,7 +2442,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2441,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2455,7 +2470,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2469,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2483,7 +2498,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2497,7 +2512,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2511,7 +2526,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2522,10 +2537,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2539,7 +2554,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2553,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2567,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2581,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2595,7 +2610,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2609,7 +2624,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2623,7 +2638,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2637,7 +2652,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2651,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2665,7 +2680,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2679,7 +2694,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2693,7 +2708,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2707,7 +2722,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2721,7 +2736,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2735,7 +2750,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2749,7 +2764,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2763,7 +2778,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2777,7 +2792,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2791,7 +2806,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2802,10 +2817,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2819,7 +2834,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2833,7 +2848,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2847,7 +2862,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2861,7 +2876,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2875,7 +2890,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2889,7 +2904,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2903,7 +2918,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2917,7 +2932,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2931,7 +2946,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2945,7 +2960,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2959,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2973,7 +2988,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2987,7 +3002,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2998,10 +3013,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3015,7 +3030,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3029,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3043,7 +3058,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3057,7 +3072,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3071,7 +3086,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3085,7 +3100,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3099,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3113,7 +3128,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3127,7 +3142,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3141,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3155,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3183,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3197,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3211,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3225,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3239,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>350</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3253,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3267,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3281,7 +3296,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3295,7 +3310,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3309,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3323,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3337,7 +3352,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>355</v>
+        <v>283</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3351,7 +3366,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3365,7 +3380,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3379,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3393,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3407,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3421,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3435,7 +3450,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3449,7 +3464,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3463,7 +3478,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3477,7 +3492,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3491,7 +3506,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3505,7 +3520,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3519,7 +3534,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3533,7 +3548,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3547,7 +3562,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3561,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3575,7 +3590,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3589,7 +3604,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3603,7 +3618,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3617,7 +3632,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3631,7 +3646,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3645,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3659,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3673,7 +3688,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3687,7 +3702,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3701,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3715,7 +3730,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3726,10 +3741,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3743,7 +3758,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3757,7 +3772,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3771,7 +3786,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3785,7 +3800,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3799,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3813,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3827,7 +3842,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3841,7 +3856,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3855,7 +3870,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3869,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3883,7 +3898,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3897,7 +3912,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3911,7 +3926,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3925,7 +3940,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3936,10 +3951,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3953,7 +3968,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>393</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3967,7 +3982,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3981,7 +3996,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3995,7 +4010,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4009,7 +4024,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4023,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4037,7 +4052,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4051,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4065,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4079,7 +4094,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4093,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4107,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4121,7 +4136,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4135,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>315</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4149,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>407</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4163,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4177,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4191,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4205,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4219,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4230,10 +4245,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4247,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4261,7 +4276,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4272,10 +4287,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4289,7 +4304,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4303,7 +4318,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4317,7 +4332,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>270</v>
+        <v>417</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4331,7 +4346,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4345,7 +4360,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4359,7 +4374,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4373,7 +4388,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4387,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4401,7 +4416,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4415,7 +4430,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4429,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4443,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4457,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4471,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4485,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4499,7 +4514,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4513,7 +4528,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4524,10 +4539,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4538,10 +4553,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4555,7 +4570,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4566,10 +4581,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4580,10 +4595,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4597,7 +4612,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4611,7 +4626,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4625,7 +4640,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4636,10 +4651,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4653,7 +4668,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4667,7 +4682,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4681,7 +4696,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4695,7 +4710,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4709,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4723,7 +4738,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4737,7 +4752,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4751,7 +4766,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4765,7 +4780,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4779,7 +4794,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4793,7 +4808,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4807,7 +4822,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4821,7 +4836,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4835,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4849,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4863,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>449</v>
+        <v>416</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4877,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4891,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4905,7 +4920,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4916,10 +4931,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4930,10 +4945,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4947,7 +4962,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4961,7 +4976,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4975,7 +4990,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4989,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>457</v>
+        <v>326</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5003,7 +5018,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5017,7 +5032,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5031,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5045,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5059,7 +5074,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5073,7 +5088,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>273</v>
+        <v>467</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5087,7 +5102,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5101,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>269</v>
+        <v>469</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5115,7 +5130,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>346</v>
+        <v>271</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5129,7 +5144,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5143,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5157,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5171,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5185,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>272</v>
+        <v>469</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5199,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5213,7 +5228,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5227,7 +5242,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5241,7 +5256,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5255,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5269,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5283,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5297,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5311,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5325,7 +5340,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5339,7 +5354,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5353,7 +5368,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5367,7 +5382,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5381,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>478</v>
+        <v>389</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5395,7 +5410,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
